--- a/Input/File_001.xlsx
+++ b/Input/File_001.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>链接</t>
   </si>
@@ -60,48 +60,6 @@
   </si>
   <si>
     <t>magnet:?xt=urn:btih:3713d6a5b1318beaff888c2a1349e61464b1a12b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:604c11a109de941870584a82be4d439cc9a587ce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:833401f94785cf5491ffee12a0452c5c07cfb703</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0b8eeae0b1f790b25af6227aecdc412cd9329f87</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c8fe0cb81031e385c53704e70659e178e5e38bee</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d377acfc2545b0cf4ca66f4420d563d18cccaf41</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35f52bda716278ec0b2049f7745da182c1957e2a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9941f76456bfaf8794c61fedff698753fbff922d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e34b75809b00949489fe36f9300c8a1c05807567</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f7c1b76c58f1990bb2ea1199a1ca3bb1717cfc9c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a6a45874e6f0dd2af5d8f3b1e8c3f22cb71d234</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:00ba10e716f1e18922931546d62f236013b747d8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ae7e7df6b79a47a916126dd20f46400ecb26899f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5599215f01e9b3ec77bed2fb406e6c04d81090c9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a56a349215f117543a5805302d41a6473889450</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:5">
@@ -1297,76 +1255,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-    </row>
+    <row r="8" s="1" customFormat="1"/>
+    <row r="9" s="1" customFormat="1"/>
+    <row r="10" s="1" customFormat="1"/>
+    <row r="11" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
